--- a/data/trans_dic/IP2906_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP2906_2023-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que recibieron lactancia mixta durante los primeros meses de vida</t>
+          <t>Menores que recibieron lactancia mixta durante los primeros meses de vida (tasa de respuesta: 98,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,1; 35,29</t>
+          <t>16,04; 35,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,65; 19,44</t>
+          <t>6,77; 19,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,23; 24,17</t>
+          <t>13,16; 23,8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>61,87; 78,01</t>
+          <t>61,63; 78,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>54,41; 73,6</t>
+          <t>54,41; 73,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60,59; 73,38</t>
+          <t>60,18; 73,5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34,18; 55,98</t>
+          <t>36,67; 57,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46,61; 66,73</t>
+          <t>45,26; 66,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44,21; 58,91</t>
+          <t>44,68; 59,23</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,39; 48,48</t>
+          <t>27,41; 48,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,84; 50,64</t>
+          <t>19,52; 49,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,06; 45,04</t>
+          <t>27,15; 45,44</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,61; 31,93</t>
+          <t>12,31; 32,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,7; 30,46</t>
+          <t>11,05; 29,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,84; 27,02</t>
+          <t>13,69; 27,34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63,65; 84,97</t>
+          <t>64,12; 84,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>55,98; 77,75</t>
+          <t>57,17; 77,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63,2; 78,44</t>
+          <t>62,93; 77,94</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,18; 33,31</t>
+          <t>18,99; 33,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19,57; 35,49</t>
+          <t>19,52; 35,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,74; 31,9</t>
+          <t>21,15; 32,19</t>
         </is>
       </c>
     </row>
@@ -921,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>40,39; 55,22</t>
+          <t>40,61; 56,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>44,07; 58,64</t>
+          <t>44,17; 58,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44,69; 55,21</t>
+          <t>44,7; 54,7</t>
         </is>
       </c>
     </row>
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>40,09; 46,81</t>
+          <t>39,98; 46,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>38,55; 46,41</t>
+          <t>39,13; 46,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40,47; 45,43</t>
+          <t>40,09; 45,5</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que recibieron lactancia mixta durante los primeros meses de vida (tasa de respuesta: 98,82%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>17693</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9034</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>26727</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>11454; 25306</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5052; 14342</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19215; 34748</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>67752</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>79980</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>147732</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>59330; 75299</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>67286; 90803</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>132359; 161670</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>25885</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>35883</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>61767</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>20535; 32044</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>28946; 42775</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>53589; 71045</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>25526</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>26350</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>51876</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>18582; 32779</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>14422; 36584</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>38457; 64369</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>7126</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7666</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>14791</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>4211; 11223</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4501; 12122</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>10254; 20479</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>32431</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>36657</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>69088</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>27435; 36334</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>30746; 41828</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>60775; 75265</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>30587</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>41323</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>71909</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>23140; 40476</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>30171; 54403</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>58475; 88980</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>61322</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>78649</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>139971</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>51765; 71544</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>67958; 90278</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>125769; 153879</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>814</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>268322</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>315541</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>583863</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>246961; 290031</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>289224; 343369</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>543972; 617390</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2906_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP2906_2023-Provincia-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,04; 35,44</t>
+          <t>15,72; 34,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,77; 19,22</t>
+          <t>6,83; 20,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,16; 23,8</t>
+          <t>13,05; 24,36</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>61,63; 78,21</t>
+          <t>61,38; 77,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>54,41; 73,42</t>
+          <t>55,18; 73,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60,18; 73,5</t>
+          <t>60,18; 72,88</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,67; 57,22</t>
+          <t>36,14; 56,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45,26; 66,88</t>
+          <t>45,35; 65,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44,68; 59,23</t>
+          <t>43,91; 58,66</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,41; 48,36</t>
+          <t>28,27; 48,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,52; 49,52</t>
+          <t>20,93; 50,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,15; 45,44</t>
+          <t>26,81; 45,81</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,31; 32,82</t>
+          <t>12,43; 31,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,05; 29,77</t>
+          <t>10,92; 29,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,69; 27,34</t>
+          <t>13,64; 27,08</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>64,12; 84,91</t>
+          <t>64,54; 84,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>57,17; 77,77</t>
+          <t>54,99; 76,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62,93; 77,94</t>
+          <t>62,67; 78,62</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,99; 33,22</t>
+          <t>18,77; 33,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19,52; 35,19</t>
+          <t>19,67; 35,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21,15; 32,19</t>
+          <t>20,97; 31,35</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>40,61; 56,13</t>
+          <t>40,64; 55,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>44,17; 58,67</t>
+          <t>43,52; 57,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44,7; 54,7</t>
+          <t>44,28; 55,1</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>39,98; 46,95</t>
+          <t>40,0; 46,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>39,13; 46,46</t>
+          <t>39,33; 46,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40,09; 45,5</t>
+          <t>40,65; 45,64</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11454; 25306</t>
+          <t>11223; 24853</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5052; 14342</t>
+          <t>5099; 14998</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19215; 34748</t>
+          <t>19051; 35564</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>59330; 75299</t>
+          <t>59092; 74982</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>67286; 90803</t>
+          <t>68247; 90825</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>132359; 161670</t>
+          <t>132359; 160302</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>20535; 32044</t>
+          <t>20237; 31527</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>28946; 42775</t>
+          <t>29004; 42205</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>53589; 71045</t>
+          <t>52672; 70365</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18582; 32779</t>
+          <t>19163; 33067</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14422; 36584</t>
+          <t>15462; 37040</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38457; 64369</t>
+          <t>37974; 64888</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4211; 11223</t>
+          <t>4251; 10847</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4501; 12122</t>
+          <t>4448; 12071</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10254; 20479</t>
+          <t>10221; 20289</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>27435; 36334</t>
+          <t>27615; 36357</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>30746; 41828</t>
+          <t>29575; 41380</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60775; 75265</t>
+          <t>60517; 75924</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>23140; 40476</t>
+          <t>22871; 40499</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>30171; 54403</t>
+          <t>30399; 54439</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>58475; 88980</t>
+          <t>57970; 86658</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>51765; 71544</t>
+          <t>51798; 70502</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>67958; 90278</t>
+          <t>66959; 88719</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>125769; 153879</t>
+          <t>124580; 155002</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>246961; 290031</t>
+          <t>247107; 288013</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>289224; 343369</t>
+          <t>290695; 342775</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>543972; 617390</t>
+          <t>551504; 619270</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2906_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP2906_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,72; 34,81</t>
+          <t>7,44; 21,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,83; 20,1</t>
+          <t>20,64; 39,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,05; 24,36</t>
+          <t>15,21; 26,77</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>66,46%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>61,38; 77,88</t>
+          <t>53,58; 73,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55,18; 73,44</t>
+          <t>60,34; 77,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60,18; 72,88</t>
+          <t>59,97; 72,65</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,78%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,14; 56,3</t>
+          <t>47,12; 66,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45,35; 65,99</t>
+          <t>35,08; 56,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43,91; 58,66</t>
+          <t>44,69; 59,45</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>37,89%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,27; 48,78</t>
+          <t>22,8; 52,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,93; 50,14</t>
+          <t>27,8; 49,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,81; 45,81</t>
+          <t>28,6; 46,2</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,43; 31,72</t>
+          <t>10,54; 29,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,92; 29,65</t>
+          <t>11,88; 30,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,64; 27,08</t>
+          <t>13,29; 25,61</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>72,16%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>64,54; 84,97</t>
+          <t>56,11; 77,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>54,99; 76,94</t>
+          <t>64,61; 85,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62,67; 78,62</t>
+          <t>64,55; 79,39</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,77; 33,24</t>
+          <t>22,02; 38,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19,67; 35,22</t>
+          <t>17,68; 30,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,97; 31,35</t>
+          <t>21,61; 32,58</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,72%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>40,64; 55,31</t>
+          <t>43,89; 58,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>43,52; 57,66</t>
+          <t>40,39; 55,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44,28; 55,1</t>
+          <t>44,55; 55,22</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>40,0; 46,62</t>
+          <t>39,61; 47,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>39,33; 46,38</t>
+          <t>40,6; 47,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40,65; 45,64</t>
+          <t>41,44; 46,23</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17693</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9034</t>
+          <t>16199</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26727</t>
+          <t>24024</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11223; 24853</t>
+          <t>4485; 12694</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5099; 14998</t>
+          <t>11334; 21952</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19051; 35564</t>
+          <t>17524; 30830</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>93</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>67752</t>
+          <t>72393</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>79980</t>
+          <t>64864</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>147732</t>
+          <t>137257</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>59092; 74982</t>
+          <t>60238; 82478</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68247; 90825</t>
+          <t>56769; 72537</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>132359; 160302</t>
+          <t>123851; 150032</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>45</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25885</t>
+          <t>32030</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35883</t>
+          <t>25562</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61767</t>
+          <t>57592</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>20237; 31527</t>
+          <t>26704; 37921</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29004; 42205</t>
+          <t>19133; 30951</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52672; 70365</t>
+          <t>49702; 66118</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>25526</t>
+          <t>25554</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>26350</t>
+          <t>26289</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51876</t>
+          <t>51843</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19163; 33067</t>
+          <t>15594; 35948</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15462; 37040</t>
+          <t>19024; 33772</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37974; 64888</t>
+          <t>39130; 63199</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7126</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7666</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14791</t>
+          <t>14306</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4251; 10847</t>
+          <t>4172; 11532</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4448; 12071</t>
+          <t>4200; 10913</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10221; 20289</t>
+          <t>9958; 19191</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>55</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>32431</t>
+          <t>32230</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>36657</t>
+          <t>32705</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>69088</t>
+          <t>64935</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>27615; 36357</t>
+          <t>26490; 36799</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29575; 41380</t>
+          <t>27641; 36504</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60517; 75924</t>
+          <t>58088; 71441</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>30587</t>
+          <t>41083</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>41323</t>
+          <t>28209</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>71909</t>
+          <t>69292</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>22871; 40499</t>
+          <t>30857; 53940</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>30399; 54439</t>
+          <t>21184; 36447</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>57970; 86658</t>
+          <t>56167; 84699</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>61322</t>
+          <t>80085</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>78649</t>
+          <t>65421</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>139971</t>
+          <t>145505</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>51798; 70502</t>
+          <t>68755; 91432</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>66959; 88719</t>
+          <t>54927; 75413</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>124580; 155002</t>
+          <t>130363; 161607</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>401</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>413</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>268322</t>
+          <t>298448</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>315541</t>
+          <t>266306</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>583863</t>
+          <t>564755</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>247107; 288013</t>
+          <t>269880; 323279</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>290695; 342775</t>
+          <t>245993; 285743</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>551504; 619270</t>
+          <t>533428; 595068</t>
         </is>
       </c>
     </row>
